--- a/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N5_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T5171_W0014F0003T0006Z000C1N5_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>53.02404469825606</v>
+        <v>8.616407263466609</v>
       </c>
       <c r="D2" t="n">
-        <v>52.9260975362154</v>
+        <v>8.600490849635003</v>
       </c>
       <c r="E2" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F2" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>48.9322311252423</v>
+        <v>7.951487557851873</v>
       </c>
       <c r="D3" t="n">
-        <v>48.66850796387038</v>
+        <v>7.908632544128936</v>
       </c>
       <c r="E3" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F3" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>52.56810483455383</v>
+        <v>8.542317035614998</v>
       </c>
       <c r="D4" t="n">
-        <v>52.27966485387541</v>
+        <v>8.495445538754755</v>
       </c>
       <c r="E4" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F4" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>35.59640426718552</v>
+        <v>5.784415693417647</v>
       </c>
       <c r="D5" t="n">
-        <v>35.34964375352339</v>
+        <v>5.744317109947551</v>
       </c>
       <c r="E5" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F5" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>39.44453111655765</v>
+        <v>6.409736306440618</v>
       </c>
       <c r="D6" t="n">
-        <v>20.42311313918272</v>
+        <v>3.318755885117193</v>
       </c>
       <c r="E6" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F6" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.97430489813241</v>
+        <v>4.870824545946516</v>
       </c>
       <c r="D7" t="n">
-        <v>29.67893726299241</v>
+        <v>4.822827305236267</v>
       </c>
       <c r="E7" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F7" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>31.001484102179</v>
+        <v>5.037741166604088</v>
       </c>
       <c r="D8" t="n">
-        <v>25.36820565172408</v>
+        <v>4.122333418405163</v>
       </c>
       <c r="E8" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F8" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.4328582607865</v>
+        <v>6.082839467377806</v>
       </c>
       <c r="D9" t="n">
-        <v>37.16424685558169</v>
+        <v>6.039190114032024</v>
       </c>
       <c r="E9" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F9" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>28.93591601516025</v>
+        <v>4.702086352463541</v>
       </c>
       <c r="D10" t="n">
-        <v>27.69107903257231</v>
+        <v>4.499800342793</v>
       </c>
       <c r="E10" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F10" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.41602361921509</v>
+        <v>6.242603838122452</v>
       </c>
       <c r="D11" t="n">
-        <v>21.38492667177974</v>
+        <v>3.475050584164208</v>
       </c>
       <c r="E11" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F11" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>27.07712587114428</v>
+        <v>4.400032954060946</v>
       </c>
       <c r="D12" t="n">
-        <v>25.92778432492835</v>
+        <v>4.213264952800857</v>
       </c>
       <c r="E12" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F12" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>49.65100809209908</v>
+        <v>8.068288814966101</v>
       </c>
       <c r="D13" t="n">
-        <v>13.46622660116256</v>
+        <v>2.188261822688916</v>
       </c>
       <c r="E13" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F13" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.463591973397</v>
+        <v>6.737833695677013</v>
       </c>
       <c r="D14" t="n">
-        <v>11.73562128223187</v>
+        <v>1.90703845836268</v>
       </c>
       <c r="E14" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F14" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>53.4849993642563</v>
+        <v>8.691312396691648</v>
       </c>
       <c r="D15" t="n">
-        <v>4.609772228646444</v>
+        <v>0.7490879871550471</v>
       </c>
       <c r="E15" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F15" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>33.11390331989424</v>
+        <v>5.381009289482814</v>
       </c>
       <c r="D16" t="n">
-        <v>33.08478919187348</v>
+        <v>5.37627824367944</v>
       </c>
       <c r="E16" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F16" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>47.55901367569534</v>
+        <v>7.728339722300493</v>
       </c>
       <c r="D17" t="n">
-        <v>47.43296401512863</v>
+        <v>7.707856652458403</v>
       </c>
       <c r="E17" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F17" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>52.56585776622755</v>
+        <v>8.541951887011978</v>
       </c>
       <c r="D18" t="n">
-        <v>52.51971407370083</v>
+        <v>8.534453536976384</v>
       </c>
       <c r="E18" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F18" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>52.90733990193336</v>
+        <v>8.597442734064172</v>
       </c>
       <c r="D19" t="n">
-        <v>52.90361742680719</v>
+        <v>8.596837831856169</v>
       </c>
       <c r="E19" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F19" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1056,16 +1056,16 @@
         <v>19</v>
       </c>
       <c r="C20" t="n">
-        <v>50.82252762583065</v>
+        <v>8.258660739197481</v>
       </c>
       <c r="D20" t="n">
-        <v>36.69468626381754</v>
+        <v>5.962886517870351</v>
       </c>
       <c r="E20" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F20" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>55.34274106129777</v>
+        <v>8.993195422460888</v>
       </c>
       <c r="D21" t="n">
-        <v>49.48989795907848</v>
+        <v>8.042108418350253</v>
       </c>
       <c r="E21" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F21" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1120,16 +1120,16 @@
         <v>21</v>
       </c>
       <c r="C22" t="n">
-        <v>58.3699331658806</v>
+        <v>9.485114139455597</v>
       </c>
       <c r="D22" t="n">
-        <v>40.57599040975372</v>
+        <v>6.59359844158498</v>
       </c>
       <c r="E22" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F22" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1152,16 +1152,16 @@
         <v>22</v>
       </c>
       <c r="C23" t="n">
-        <v>60.17468806254114</v>
+        <v>9.778386810162937</v>
       </c>
       <c r="D23" t="n">
-        <v>29.49510034786892</v>
+        <v>4.7929538065287</v>
       </c>
       <c r="E23" t="n">
-        <v>10.16895565194211</v>
+        <v>1.652455293440592</v>
       </c>
       <c r="F23" t="n">
-        <v>14.19729673509985</v>
+        <v>2.307060719453726</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
